--- a/附录1：测试用例清单（模块二）.xlsx
+++ b/附录1：测试用例清单（模块二）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="300" windowWidth="12120" windowHeight="9000" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Information文档信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Test Cases测试用例" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Introduction使用说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information文档信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases测试用例" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Introduction使用说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Result">'Test Cases测试用例'!$N$2:$N$5</definedName>
@@ -664,13 +664,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t/>
             </a:r>
@@ -689,16 +689,16 @@
       </layout>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="25400">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1050" b="0" i="0" strike="noStrike" baseline="0">
               <a:solidFill>
@@ -739,7 +739,7 @@
             <v>测试结果</v>
           </tx>
           <spPr>
-            <a:ln w="25400">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -748,10 +748,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9999FF"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -761,10 +761,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="993366"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -774,10 +774,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="808000"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -787,10 +787,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="FFCC99"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -865,10 +865,10 @@
       </layout>
       <overlay val="0"/>
       <spPr>
-        <a:solidFill>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="3175">
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
@@ -876,9 +876,9 @@
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="965" b="0" i="0" strike="noStrike" baseline="0">
               <a:solidFill>
@@ -900,10 +900,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="3175">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
       <a:solidFill>
         <a:srgbClr val="000000"/>
       </a:solidFill>
@@ -914,7 +914,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -934,12 +934,56 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>9525</colOff>
+      <row>0</row>
+      <rowOff>104775</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>95250</colOff>
+      <row>2</row>
+      <rowOff>57150</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2056" name="Picture 4"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="152400" y="104775"/>
+          <a:ext cx="2828925" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
     <clientData/>
   </twoCellAnchor>
 </wsDr>
@@ -1309,7 +1353,7 @@
       <c r="I7" s="9" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K7" s="11" t="n"/>
@@ -1367,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1396,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1425,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1451,9 +1495,8 @@
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
-      <c r="E13" s="13">
-        <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v/>
+      <c r="E13" s="13" t="n">
+        <v>20</v>
       </c>
       <c r="F13" s="10" t="n"/>
     </row>
@@ -1484,7 +1527,7 @@
       <c r="B16" s="58" t="inlineStr">
         <is>
           <t>本清单为【模块二·AI 融合实践（方案 2"AI 测"）】交付件，被测对象与模块一相同：2024 种子杯机械臂避障抓取赛项的"算法核心模块"——team_algorithm.py 的 MyCustomAlgorithm 类及其运动学辅助函数。
-共 20 条用例，是在模块一 30 条的基础上借助 AI 工具扩展生成的：由 AI 提出用例方向、构造输入观测、推演预期值并生成检查函数，小组逐条核对测试预言，剔除与 URDF / env.py 契约不符的臆测。用例集中在模块一未覆盖的深水区——运动学正解与连杆姿态、末端夹爪中心模型、距离度量的代数性质、避障判定表的全部阈值边界点、构造参数的白盒覆盖、逆解数值健壮性与关节限幅；判定每一条都需要 URDF 关节链、旋转矩阵或数值容差方面的专门知识。
+共 20 条用例，是在模块一 34 条的基础上借助 AI 工具扩展生成的：由 AI 提出用例方向、构造输入观测、推演预期值并生成检查函数，小组逐条核对测试预言，剔除与 URDF / env.py 契约不符的臆测。用例集中在模块一未覆盖的深水区——运动学正解与连杆姿态、末端夹爪中心模型、距离度量的代数性质、避障判定表的全部阈值边界点、构造参数的白盒覆盖、逆解数值健壮性与关节限幅；判定每一条都需要 URDF 关节链、旋转矩阵或数值容差方面的专门知识。
 AI 辅助与人工修正的关键差异、以及 AI 输出中的错误与遗漏（典型如 TC-ALG-036 因被测接口变更而失效），见《附录4：测试报告（模块二）》。
 测试预言（test oracle）不依赖被测代码，而由三处独立来源构造：① fr5_description/urdf/fr5v6.urdf 的关节链偏移与关节限位；② env.py 对外契约（观测归一化、step 动作语义、reward 判定式、get_dis 夹爪中心定义）；③ team_algorithm.py 末尾由 env.debugdoor() 打印的真实 PyBullet 输出（footnote）。
 用例全部以"纯逻辑测试 + Mock 替身"实现，由 pytest 驱动执行：以严格按 URDF 重建的参考运动学（tests/kinematics_ref.py）作为位置真值，以复现 env.py 语义的 Mock 环境（tests/mock_env.py）替代 PyBullet 物理引擎，故不依赖图形界面、任何机器上均可一键复现；真实 PyBullet（conda-forge pybullet 3.2.5）另用于 test.py 的端到端对照运行。</t>
@@ -1567,7 +1610,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -2762,12 +2805,12 @@
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t>与 env.get_dis() 夹爪中心最大偏差 0.07612 m（成功阈值 0.05 m）</t>
+          <t>与 env.get_dis() 夹爪中心最大偏差 0.00000 m（成功阈值 0.05 m）</t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">

--- a/附录1：测试用例清单（模块二）.xlsx
+++ b/附录1：测试用例清单（模块二）.xlsx
@@ -1411,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1440,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1469,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1610,7 +1610,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">

--- a/附录1：测试用例清单（模块二）.xlsx
+++ b/附录1：测试用例清单（模块二）.xlsx
@@ -1411,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1440,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1469,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1610,7 +1610,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">

--- a/附录1：测试用例清单（模块二）.xlsx
+++ b/附录1：测试用例清单（模块二）.xlsx
@@ -1411,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1440,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1469,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1496,7 +1496,7 @@
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F13" s="10" t="n"/>
     </row>
@@ -1527,7 +1527,8 @@
       <c r="B16" s="58" t="inlineStr">
         <is>
           <t>本清单为【模块二·AI 融合实践（方案 2"AI 测"）】交付件，被测对象与模块一相同：2024 种子杯机械臂避障抓取赛项的"算法核心模块"——team_algorithm.py 的 MyCustomAlgorithm 类及其运动学辅助函数。
-共 20 条用例，是在模块一 34 条的基础上借助 AI 工具扩展生成的：由 AI 提出用例方向、构造输入观测、推演预期值并生成检查函数，小组逐条核对测试预言，剔除与 URDF / env.py 契约不符的臆测。用例集中在模块一未覆盖的深水区——运动学正解与连杆姿态、末端夹爪中心模型、距离度量的代数性质、避障判定表的全部阈值边界点、构造参数的白盒覆盖、逆解数值健壮性与关节限幅；判定每一条都需要 URDF 关节链、旋转矩阵或数值容差方面的专门知识。
+共 22 条用例，是在模块一 34 条的基础上借助 AI 工具扩展生成的：由 AI 提出用例方向、构造输入观测、推演预期值并生成检查函数，小组逐条核对测试预言，剔除与 URDF / env.py 契约不符的臆测。用例集中在模块一未覆盖的深水区——运动学正解与连杆姿态、末端夹爪中心模型、距离度量的代数性质、避障判定表的全部阈值边界点、键盘微调通路的状态覆盖、观测入参的别名隔离、避障姿态的关节限位可实施性、逆解数值健壮性与关节限幅；判定每一条都需要 URDF 关节链、旋转矩阵或数值容差方面的专门知识。
+其中 TC-ALG-055（观测入参不得被就地修改）钉出了被测算法的一处真实缺陷：get_action 把观测切片按视图存入自身状态，下游键盘微调的就地写遂沿别名改写了调用方的观测。该缺陷由 AI 辅助白盒阅读定位、经人工实测确认并修复，详见《附录2：缺陷报告（模块二）》编号 006。
 AI 辅助与人工修正的关键差异、以及 AI 输出中的错误与遗漏（典型如 TC-ALG-036 因被测接口变更而失效），见《附录4：测试报告（模块二）》。
 测试预言（test oracle）不依赖被测代码，而由三处独立来源构造：① fr5_description/urdf/fr5v6.urdf 的关节链偏移与关节限位；② env.py 对外契约（观测归一化、step 动作语义、reward 判定式、get_dis 夹爪中心定义）；③ team_algorithm.py 末尾由 env.debugdoor() 打印的真实 PyBullet 输出（footnote）。
 用例全部以"纯逻辑测试 + Mock 替身"实现，由 pytest 驱动执行：以严格按 URDF 重建的参考运动学（tests/kinematics_ref.py）作为位置真值，以复现 env.py 语义的 Mock 环境（tests/mock_env.py）替代 PyBullet 物理引擎，故不依赖图形界面、任何机器上均可一键复现；真实 PyBullet（conda-forge pybullet 3.2.5）另用于 test.py 的端到端对照运行。</t>
@@ -1610,7 +1611,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -1625,7 +1626,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>initial 初稿完成：在模块一基础上由 AI 扩展生成 20 条进阶用例，人工逐条核对测试预言后以 pytest 自动化执行</t>
+          <t>initial 初稿完成：在模块一基础上由 AI 扩展生成 22 条进阶用例，人工逐条核对测试预言后以 pytest 自动化执行</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -2629,7 +2630,7 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>link 帧位置未被 URDF 质心 origin 污染</t>
+          <t>质心帧位置与 PyBullet getLinkState(i)[0] 一致</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
@@ -2649,7 +2650,7 @@
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>URDF &lt;inertial&gt; 的 origin 为质心，不能当作运动学偏移</t>
+          <t>env.get_dis 取的是质心帧 [0]，不是连杆帧 [4]；量零位须关重力并断开电机</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
@@ -2659,7 +2660,7 @@
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>比较 mats[i][2] 与 PyBullet 真值位置</t>
+          <t>比较 mats[i][2]（inertial 质心链）与 PyBullet getLinkState(i)[0] 真值</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
@@ -2669,12 +2670,12 @@
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>link 帧位置被 &lt;inertial&gt; 质心 origin 污染，与 PyBullet 实际报告不符：Link2 偏差 0.21250m，Link3 偏差 0.18793m，Link4 偏差 0.09715m，Link5 偏差 0.09826m，Link6 偏差 0.07612m，Link7 偏差 1.04500m</t>
+          <t>质心帧位置与 PyBullet getLinkState(i)[0] 一致，最大偏差 5.0e-07 m</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
@@ -3445,7 +3446,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>A5 恰为 -90 时不产生基座方向策略（边界）</t>
+          <t>键盘对瞄准点的微调：键 1/2/3 配合 9/0</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -3465,37 +3466,37 @@
       </c>
       <c r="G18" s="42" t="inlineStr">
         <is>
-          <t>判定为 A5&gt;-90 与 A5&lt;-90，两者均为严格不等</t>
+          <t>get_action 的键盘通路仅在被传入 env 时生效；不按键时不得改变输出</t>
         </is>
       </c>
       <c r="H18" s="42" t="inlineStr">
         <is>
-          <t>bdb = 40°（A5=-90）</t>
+          <t>按住 键1+键9、键2+键0，以及不按键三种情形</t>
         </is>
       </c>
       <c r="I18" s="42" t="inlineStr">
         <is>
-          <t>检查 strategies 是否含 A1Left/A1Right</t>
+          <t>传入按键替身 env 调用 get_action，读取 alg.xyz_target</t>
         </is>
       </c>
       <c r="J18" s="42" t="inlineStr">
         <is>
-          <t>两者均不含</t>
+          <t>不按键时 xyz_target 等于目标坐标；键1+9 时 x 减 0.005；键2+0 时 y 加 0.005</t>
         </is>
       </c>
       <c r="K18" s="42" t="inlineStr">
         <is>
-          <t>bdb=40.0000° A5=-90.0 时 strategies=['A1Right', 'A2Up', 'A3Up', 'A4Up']（不含 A1 方向）</t>
+          <t>无键 xyz_target=[+0.000000 +0.850000 +0.200000]；键1+9 → [-0.005000 +0.850000 +0.200000]；键2+0 → [+0.000000 +0.855000 +0.200000]</t>
         </is>
       </c>
       <c r="L18" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M18" s="42" t="inlineStr">
         <is>
-          <t>边界值分析（边界 -90）</t>
+          <t>边界值分析（不按键 / 键 9 减 / 键 0 加）</t>
         </is>
       </c>
       <c r="N18" s="43" t="n"/>
@@ -3513,7 +3514,7 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t>构造参数 DFL 强制覆盖查表姿态</t>
+          <t>键盘强制覆盖查表姿态：键 4/5/6 配合 9/0</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -3533,37 +3534,37 @@
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t>构造时传入 A4/A5/A6</t>
+          <t>bdb=10° 时 sig_reset 查表给出 A4=0、A5=-130、A6=0</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
-          <t>MyCustomAlgorithm(A4=0, A5=-30, A6=45)，bdb=10°</t>
+          <t>按住 键5+键0、键4+键9、键6+键9，以及不按键四种情形</t>
         </is>
       </c>
       <c r="I19" s="42" t="inlineStr">
         <is>
-          <t>调用 get_action 后读取 A4/A5/A6</t>
+          <t>传入按键替身 env 调用 get_action，读取 alg.A4/A5/A6</t>
         </is>
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>A4=0, A5=-30, A6=45（覆盖查表结果 A5=-130）</t>
+          <t>无键保持 A4=0、A5=-130、A6=0；键5+0 → A5=-129；键4+9 → A4=-1；键6+9 → A6=-1</t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
         <is>
-          <t>TypeError: MyCustomAlgorithm.__init__() got an unexpected keyword argument 'A4'</t>
+          <t>查表 A4=0.0 A5=-130.0 A6=0.0；键盘覆盖后 键5+0→A5=-129.0，键4+9→A4=-1.0，键6+9→A6=-1.0</t>
         </is>
       </c>
       <c r="L19" s="42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M19" s="42" t="inlineStr">
         <is>
-          <t>等价类划分（参数覆盖）</t>
+          <t>等价类划分（无键 / 键9 减 / 键0 加）</t>
         </is>
       </c>
       <c r="N19" s="43" t="n"/>
@@ -3705,35 +3706,139 @@
       <c r="N21" s="43" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="42" t="n"/>
-      <c r="B22" s="42" t="n"/>
-      <c r="C22" s="42" t="n"/>
-      <c r="D22" s="42" t="n"/>
-      <c r="E22" s="42" t="n"/>
-      <c r="F22" s="42" t="n"/>
-      <c r="G22" s="42" t="n"/>
-      <c r="H22" s="42" t="n"/>
-      <c r="I22" s="42" t="n"/>
-      <c r="J22" s="42" t="n"/>
-      <c r="K22" s="42" t="n"/>
-      <c r="L22" s="42" t="n"/>
-      <c r="M22" s="42" t="n"/>
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>TC-ALG-055</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>接口契约</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>观测入参不得被 get_action 就地修改</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E22" s="42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F22" s="42" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="G22" s="42" t="inlineStr">
+        <is>
+          <t>observation 由 env.get_observation() 构造，所有权属于评测框架</t>
+        </is>
+      </c>
+      <c r="H22" s="42" t="inlineStr">
+        <is>
+          <t>观测 (1,12)，Mock env 按住键 1 与键 9</t>
+        </is>
+      </c>
+      <c r="I22" s="42" t="inlineStr">
+        <is>
+          <t>调用 get_action(obs, env)，比对调用前后 obs 是否逐位相同，并检查内部状态与入参是否共享内存</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="inlineStr">
+        <is>
+          <t>obs 逐位不变，且内部状态不与入参共享内存</t>
+        </is>
+      </c>
+      <c r="K22" s="42" t="inlineStr">
+        <is>
+          <t>调用后 observation 逐位不变（长度 12 全等），且 self.xyz_target 与入参不共享内存</t>
+        </is>
+      </c>
+      <c r="L22" s="42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" s="42" t="inlineStr">
+        <is>
+          <t>白盒分析 + 边界值分析（含键盘微调通路）</t>
+        </is>
+      </c>
       <c r="N22" s="43" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="42" t="n"/>
-      <c r="B23" s="42" t="n"/>
-      <c r="C23" s="42" t="n"/>
-      <c r="D23" s="42" t="n"/>
-      <c r="E23" s="42" t="n"/>
-      <c r="F23" s="42" t="n"/>
-      <c r="G23" s="42" t="n"/>
-      <c r="H23" s="42" t="n"/>
-      <c r="I23" s="42" t="n"/>
-      <c r="J23" s="42" t="n"/>
-      <c r="K23" s="42" t="n"/>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="42" t="n"/>
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>TC-ALG-056</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>避障策略</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>各档避障姿态均落在 URDF 关节限位内</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F23" s="42" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="G23" s="42" t="inlineStr">
+        <is>
+          <t>关节限位取自 fr5v6.urdf（kinematics_ref.JOINT_LIMITS，弧度）</t>
+        </is>
+      </c>
+      <c r="H23" s="42" t="inlineStr">
+        <is>
+          <t>避障判定表 10 个分档出口（bdb=40/20/10/7/4/4(bda≤-0.28)/0/-10/-20/-30）</t>
+        </is>
+      </c>
+      <c r="I23" s="42" t="inlineStr">
+        <is>
+          <t>逐档取 sig_reset 选出的 A4/A5/A6 与解算后下达的 alg.target，与限位逐位比对</t>
+        </is>
+      </c>
+      <c r="J23" s="42" t="inlineStr">
+        <is>
+          <t>A4/A5/A6 在 j4/j5/j6 限位内，且 alg.target 六分量均在各自限位内</t>
+        </is>
+      </c>
+      <c r="K23" s="42" t="inlineStr">
+        <is>
+          <t>10 档姿态的 A4/A5/A6 与下达目标角全部落在 URDF 关节限位内（bdb=40°→A4=10 A5=-90 A6=0；bdb=20°→A4=10 A5=-120 A6=0；bdb=10°→A4=0 A5=-130 A6=0；bdb=7°→A4=-5 A5=-140 A6=0；bdb=4°→A4=40 A5=0 A6=0；bdb=4°→A4=15 A5=-20 A6=0；bdb=0°→A4=15 A5=-20 A6=0；bdb=-10°→A4=10 A5=-20 A6=0；bdb=-20°→A4=10 A5=-50 A6=0；bdb=-30°→A4=10 A5=-90 A6=0）；最大单关节行程 100.0°，与 100 步 × 1°/步 的预算持平</t>
+        </is>
+      </c>
+      <c r="L23" s="42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" s="42" t="inlineStr">
+        <is>
+          <t>白盒遍历 + 边界值分析（限位边界）</t>
+        </is>
+      </c>
       <c r="N23" s="43" t="n"/>
     </row>
     <row r="24">
